--- a/XAS-CDIFImplementation-revised.xlsx
+++ b/XAS-CDIFImplementation-revised.xlsx
@@ -227,7 +227,7 @@
     <t>units should be joules, product of current and particle energy.</t>
   </si>
   <si>
-    <t>xas:facility_energy</t>
+    <t>xas:facilityenergy</t>
   </si>
   <si>
     <t>current</t>
@@ -244,7 +244,7 @@
     <t>Units A/mA/microA. Facility modeled as schema:location Place on the wasGeneratedBy Event (was: contributor Role).</t>
   </si>
   <si>
-    <t>xas:facility_current</t>
+    <t>xas:facilitycurrent</t>
   </si>
   <si>
     <t>x-ray source</t>
@@ -321,7 +321,7 @@
     <t>prov:wasGeneratedBy/@type:schema:Action, prov:Activity, 'xas:AnalysisEvent'</t>
   </si>
   <si>
-    <t>xas:AnalysisEvent</t>
+    <t>xas:analysisevent</t>
   </si>
   <si>
     <t>CalibrationDescription</t>
@@ -357,7 +357,7 @@
     <t>xas:installedOptions in property vocabulary. Can thes options be represented as instrument components (e.g. see all the things in the NXinstrument group in NEXUS)</t>
   </si>
   <si>
-    <t>xas:installedOptions</t>
+    <t>xas:installedoptions</t>
   </si>
   <si>
     <t>Environmental conditions</t>
@@ -392,7 +392,7 @@
    schema:additionalType + schema:additionalProperty (see rows below)</t>
   </si>
   <si>
-    <t>xas:Instrument</t>
+    <t>xas:instrument</t>
   </si>
   <si>
     <t>Instrument/name</t>
@@ -500,7 +500,7 @@
     <t>partOf xas:Instrument, IsA xas:Instrument.  How is XDI beamline related to NEXUS NXbeam?</t>
   </si>
   <si>
-    <t>xas:Beamline</t>
+    <t>xas:beamline</t>
   </si>
   <si>
     <t>Instrument/beamline/name</t>
@@ -545,7 +545,7 @@
     <t>xas:harmonic_rejection in property vocabulary</t>
   </si>
   <si>
-    <t>xas:harmonic_rejection</t>
+    <t>xas:harmonicrejection</t>
   </si>
   <si>
     <t>Instrument/monitor</t>
@@ -590,7 +590,7 @@
     <t>in the instrument section, list the various detectors used to measure incident and transmitted or fluorescent intensity/flux</t>
   </si>
   <si>
-    <t>xas:detector_type</t>
+    <t>xas:detectortype</t>
   </si>
   <si>
     <t>Instrument/detector/i0</t>
@@ -623,7 +623,7 @@
     <t>schema:variableMeasured/@type=cdi:InstanceVariable/{..."schema:propertyID": {"@id": "xas:Reference_Intensity"},schema:measurementTechnique:{"@id":"uri for detector type instance"}</t>
   </si>
   <si>
-    <t>xas:Reference_Intensity</t>
+    <t>xas:referenceintensity</t>
   </si>
   <si>
     <t>Sample</t>
@@ -666,7 +666,7 @@
                     schema:additionalType: MaterialSample, additionalProperty:{ schema:propertyID: 'xas:sample_preparation',</t>
   </si>
   <si>
-    <t>xas:sample_preparation</t>
+    <t>xas:samplepreparation</t>
   </si>
   <si>
     <t>sample/size</t>
@@ -712,7 +712,7 @@
                     schema:additionalType: MaterialSample, additionalProperty:{ schema:propertyID: 'xas:parent_sample',</t>
   </si>
   <si>
-    <t>xas:parent_sample</t>
+    <t>xas:parentsample</t>
   </si>
   <si>
     <t>sample/state</t>
@@ -725,7 +725,7 @@
     <t>Suggest using material type vocabulary like https://vocabs.ardc.edu.au/viewById/664</t>
   </si>
   <si>
-    <t>xas:sample_material</t>
+    <t>xas:samplematerial</t>
   </si>
   <si>
     <t>Scan.number</t>

--- a/XAS-CDIFImplementation-revised.xlsx
+++ b/XAS-CDIFImplementation-revised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\CDIF\XAS-CDIF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04F863A-2639-446B-A45D-47889C5E5031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E4F432-C755-4B8E-9C61-B85C66965FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="2190" windowWidth="21810" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1680" windowWidth="26520" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CDIF xas implementation" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="315">
   <si>
     <t>XAS field</t>
   </si>
@@ -377,19 +377,6 @@
   </si>
   <si>
     <t>Instrument</t>
-  </si>
-  <si>
-    <t>prov:wasGeneratedBy/prov:used[0]/"schema:instrument": {
-    "@type": ["schema:Thing", "schema:Product"],
-    "schema:additionalType": "nxs:BaseClass/NXinstrument",
-    "schema:name": "(instrument system name)",
-    "schema:hasPart": [
-        { ...NXsource... }, { ...NXmonochromator... },
-        { ...xas:Beamline... }, { ...NXmonitor... }, { ...NXdetector... }
-    ]
-}  -- instrument system; each component (source, monochromator, beamline,
-   monitor, detector) is a schema:hasPart item carrying its own
-   schema:additionalType + schema:additionalProperty (see rows below)</t>
   </si>
   <si>
     <t>xas:instrument</t>
@@ -1262,6 +1249,25 @@
   </si>
   <si>
     <t>in NXxas, this identifies the profile implemented by the containing record.</t>
+  </si>
+  <si>
+    <t>prov:wasGeneratedBy/prov:used[0]/"schema:instrument": {
+    "@type": ["schema:Thing", "schema:Product"],
+    "schema:additionalType": "nxs:BaseClass/NXinstrument",
+    "schema:name": "(instrument  name)",
+    "schema:hasPart": [
+        { ...NXsource... }, { ...NXmonochromator... },
+        { ...xas:Beamline... }, { ...NXmonitor... }, { ...NXdetector... }
+    ]
+}  -- instrument can be represented as a system with parts-- each component (source, monochromator, beamline,
+   monitor, detector) is a schema:hasPart item carrying its own
+   schema:additionalType + schema:additionalProperty, or the system can be represented as a list of instruments in the schema:instrument element.</t>
+  </si>
+  <si>
+    <t>NeXus</t>
+  </si>
+  <si>
+    <t>nxdl:NXxas_trans/ENTRY:NXentry/intensity</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1471,17 +1477,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1829,25 +1826,25 @@
     <col min="1" max="1" width="32.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="23" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="51.7109375" style="14" customWidth="1"/>
+    <col min="4" max="4" width="59.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="30.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -1874,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
@@ -1894,7 +1891,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -1929,7 +1926,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>21</v>
@@ -1939,7 +1936,6 @@
       <c r="A6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="16"/>
       <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1976,7 +1972,7 @@
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>32</v>
@@ -1985,11 +1981,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="16"/>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2001,15 +1996,14 @@
       </c>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="16"/>
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -2026,11 +2020,10 @@
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="16"/>
       <c r="C11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -2080,7 +2073,7 @@
         <v>54</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2090,7 +2083,7 @@
       <c r="C14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -2117,7 +2110,7 @@
         <v>62</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2154,18 +2147,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="1"/>
-    </row>
     <row r="20" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -2210,7 +2197,7 @@
       <c r="C23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -2220,7 +2207,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>83</v>
       </c>
@@ -2237,61 +2224,58 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="315" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
@@ -2300,18 +2284,18 @@
         <v>19</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
@@ -2320,18 +2304,18 @@
         <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="1">
         <v>1</v>
@@ -2340,54 +2324,54 @@
         <v>19</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
@@ -2396,15 +2380,15 @@
         <v>19</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="1">
         <v>1</v>
@@ -2413,244 +2397,241 @@
         <v>84</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="F38" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="14" t="s">
+      <c r="E40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="14" t="s">
+      <c r="F41" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="F42" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="E46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="14" t="s">
+      <c r="F47" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="14" t="s">
+      <c r="F48" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>164</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="14" t="s">
+      <c r="F50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B52" s="4"/>
       <c r="D52" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
@@ -2659,157 +2640,157 @@
         <v>7</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="14" t="s">
+      <c r="G56" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G61" s="1" t="s">
+    </row>
+    <row r="62" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
+      <c r="B62" s="13"/>
+      <c r="C62" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F62" s="1" t="s">
+    </row>
+    <row r="63" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+      <c r="B63" s="13"/>
+      <c r="C63" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15" t="s">
+      <c r="D63" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2822,790 +2803,797 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" ht="225" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="3" spans="1:6" ht="225" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="D3" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="195" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="E4" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" ht="165" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="C5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D5" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" ht="180" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="180" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="C6" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="D6" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="C7" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="D7" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="C8" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="D8" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="C9" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="D9" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="C10" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="D10" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="C11" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="D11" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="C12" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="D12" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="C13" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="D13" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="C14" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="D14" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="C15" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="D15" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="C16" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="D16" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="C17" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="D17" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="C18" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="D18" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="C19" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="D19" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="C20" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="D20" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="C21" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="B23" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="E23" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="B24" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="B25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="B26" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="B27" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D27" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="B28" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-    </row>
-    <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="B30" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="B31" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="B32" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="B33" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D33" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="B34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="D34" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="B35" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="D35" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="B36" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="B37" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="B38" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D38" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="B39" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="B40" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D40" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="B41" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="B42" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D42" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="B43" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="B44" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>211</v>
+      <c r="D44" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>210</v>
       </c>
       <c r="F44" s="1"/>
     </row>
